--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484254_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484254_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0576</v>
+        <v>6.9155</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7879</v>
+        <v>4.4551</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2698</v>
+        <v>2.4604</v>
       </c>
       <c r="G2" t="n">
         <v>3.8109</v>
@@ -610,13 +610,13 @@
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3709</v>
+        <v>0.487</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9546</v>
+        <v>-0.2874</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5837</v>
+        <v>0.7744</v>
       </c>
       <c r="V2" t="n">
         <v>0.6642</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.84</v>
+        <v>5.7608</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0316</v>
+        <v>3.4154</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8084</v>
+        <v>2.3454</v>
       </c>
       <c r="G3" t="n">
         <v>-3.4153</v>
@@ -688,13 +688,13 @@
         <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8413</v>
+        <v>0.7621</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4153</v>
+        <v>-0.0315</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2566</v>
+        <v>0.7936</v>
       </c>
       <c r="V3" t="n">
         <v>5.4838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.966</v>
+        <v>1.1021</v>
       </c>
       <c r="E4" t="n">
         <v>1.1833</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2173</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.2906</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2532</v>
+        <v>0.3893</v>
       </c>
       <c r="T4" t="n">
         <v>0.2642</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0111</v>
+        <v>0.1251</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5545</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8583</v>
+        <v>1.0454</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5971</v>
+        <v>-0.2738</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4554</v>
+        <v>1.3192</v>
       </c>
       <c r="G5" t="n">
         <v>1.2288</v>
@@ -844,13 +844,13 @@
         <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1789</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4635</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6079</v>
+        <v>0.4718</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3869</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8338</v>
+        <v>-0.2908</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1866</v>
+        <v>-2.3375</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0204</v>
+        <v>2.0467</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5656</v>
+        <v>-0.3917</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0934</v>
+        <v>-0.3106</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4722</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.797</v>
+        <v>0.4227</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3252</v>
+        <v>-0.3057</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4718</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.8144</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7682</v>
+        <v>-0.0049</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-0.8095</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3408</v>
+        <v>0.4134</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3098</v>
+        <v>0.3653</v>
       </c>
       <c r="U6" t="n">
-        <v>1.031</v>
+        <v>0.0481</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4062</v>
+        <v>-0.5138</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.599</v>
+        <v>-1.935</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1927</v>
+        <v>1.4213</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8667</v>
+        <v>-2.5656</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4418</v>
+        <v>-2.0934</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3085</v>
+        <v>-0.4722</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0827</v>
+        <v>-1.797</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0422</v>
+        <v>-1.3252</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-0.4718</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9494</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3996</v>
+        <v>-0.7682</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.349</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5739</v>
+        <v>0.9932</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1899</v>
+        <v>0.5614</v>
       </c>
       <c r="U7" t="n">
-        <v>0.384</v>
+        <v>0.4318</v>
       </c>
       <c r="V7" t="n">
         <v>0.2772</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6431</v>
+        <v>-0.758</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4991</v>
+        <v>-1.8418</v>
       </c>
       <c r="F8" t="n">
-        <v>1.856</v>
+        <v>1.0838</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3917</v>
+        <v>-0.8667</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3106</v>
+        <v>0.4418</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-1.3085</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4227</v>
+        <v>0.0827</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3057</v>
+        <v>0.0422</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7284</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8144</v>
+        <v>-0.9494</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0049</v>
+        <v>0.3996</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8095</v>
+        <v>-1.349</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0612</v>
+        <v>0.2222</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2037</v>
+        <v>-0.0529</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1425</v>
+        <v>0.2751</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8235</v>
+        <v>-1.2063</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4959</v>
+        <v>-3.042</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6723</v>
+        <v>1.8358</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7652</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3361</v>
+        <v>0.9533</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3098</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0263</v>
+        <v>0.1897</v>
       </c>
       <c r="V9" t="n">
         <v>0.9962</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0183</v>
+        <v>-1.4465</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0352</v>
+        <v>-1.0544</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9831</v>
+        <v>-0.3921</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7004</v>
+        <v>0.4762</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2576</v>
+        <v>-0.3602</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4428</v>
+        <v>0.8364</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.672</v>
+        <v>1.7942</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6357</v>
+        <v>0.5526</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3077</v>
+        <v>1.2416</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0283</v>
+        <v>-1.318</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8933</v>
+        <v>-0.9127</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.135</v>
+        <v>-0.4052</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.8836</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.236</v>
+        <v>-0.0159</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3631</v>
+        <v>-0.4023</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1271</v>
+        <v>0.3864</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3183</v>
+        <v>-1.7671</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.681</v>
+        <v>-0.9746</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6372</v>
+        <v>-0.7925</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4762</v>
+        <v>-1.7004</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3602</v>
+        <v>-0.2576</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8364</v>
+        <v>-1.4428</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7942</v>
+        <v>-0.672</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5526</v>
+        <v>0.6357</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2416</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.318</v>
+        <v>-1.0283</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9127</v>
+        <v>-0.8933</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4052</v>
+        <v>-0.135</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1255</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8875999999999999</v>
+        <v>0.0151</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0289</v>
+        <v>-0.3026</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1413</v>
+        <v>0.3177</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3277</v>
+        <v>-3.9149</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8777</v>
+        <v>-0.6555</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4501</v>
+        <v>-3.2594</v>
       </c>
       <c r="G12" t="n">
         <v>-1.541</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4314</v>
+        <v>-0.0186</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1899</v>
+        <v>0.4121</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6213</v>
+        <v>-0.4307</v>
       </c>
       <c r="V12" t="n">
         <v>-2.16</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.018600000000003</v>
+        <v>4.926399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9688</v>
+        <v>-3.0608</v>
       </c>
       <c r="F13" t="n">
-        <v>7.9873</v>
+        <v>7.987400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-7.439399999999999</v>
@@ -1468,10 +1468,10 @@
         <v>19.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3017</v>
+        <v>4.2093</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08139999999999964</v>
+        <v>0.8264</v>
       </c>
       <c r="U13" t="n">
         <v>3.383</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6387</v>
+        <v>4.7089</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3036</v>
+        <v>4.1013</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3352</v>
+        <v>0.6075</v>
       </c>
       <c r="G14" t="n">
         <v>4.4895</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4099</v>
+        <v>-0.3398</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2667</v>
+        <v>-0.4689</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1432</v>
+        <v>0.1292</v>
       </c>
       <c r="V14" t="n">
         <v>1.3405</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3832</v>
+        <v>3.8177</v>
       </c>
       <c r="E15" t="n">
         <v>2.4775</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9058</v>
+        <v>1.3402</v>
       </c>
       <c r="G15" t="n">
         <v>4.9703</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9778</v>
+        <v>-0.5433</v>
       </c>
       <c r="T15" t="n">
         <v>-0.6987</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.279</v>
+        <v>0.1554</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0687</v>
+        <v>2.97</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4023</v>
+        <v>0.6045</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6664</v>
+        <v>2.3655</v>
       </c>
       <c r="G16" t="n">
         <v>1.4733</v>
@@ -1702,13 +1702,13 @@
         <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0568</v>
+        <v>-0.1555</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9876</v>
+        <v>-0.7853</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9308</v>
+        <v>0.6299</v>
       </c>
       <c r="V16" t="n">
         <v>2.8242</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2118</v>
+        <v>-0.1744</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8668</v>
+        <v>-0.7608</v>
       </c>
       <c r="F17" t="n">
-        <v>2.655</v>
+        <v>0.5864</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7264</v>
+        <v>2.7514</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9939</v>
+        <v>-0.0808</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2675</v>
+        <v>2.8322</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0312</v>
+        <v>2.7064</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2975</v>
+        <v>0.1433</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2663</v>
+        <v>2.5632</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3048</v>
+        <v>0.045</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3036</v>
+        <v>-0.2241</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0012</v>
+        <v>0.269</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.2975</v>
+        <v>-3.3208</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7175</v>
+        <v>-0.6803</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1185</v>
+        <v>-0.1464</v>
       </c>
       <c r="U17" t="n">
-        <v>0.599</v>
+        <v>-0.5339</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4837</v>
+        <v>-0.4875</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7647</v>
+        <v>-0.4875</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5169</v>
+        <v>-0.4896</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0605</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4563</v>
+        <v>-0.4291</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4745</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1416</v>
+        <v>-0.9094</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2664</v>
+        <v>-3.3723</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1248</v>
+        <v>2.4629</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7514</v>
+        <v>1.7264</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0808</v>
+        <v>2.9939</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8322</v>
+        <v>-1.2675</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7064</v>
+        <v>2.0312</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1433</v>
+        <v>3.2975</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5632</v>
+        <v>-1.2663</v>
       </c>
       <c r="M19" t="n">
-        <v>0.045</v>
+        <v>-0.3048</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2241</v>
+        <v>-0.3036</v>
       </c>
       <c r="O19" t="n">
-        <v>0.269</v>
+        <v>-0.0012</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7581</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3208</v>
+        <v>-4.2975</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6475</v>
+        <v>0.0199</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.652</v>
+        <v>-0.387</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9955000000000001</v>
+        <v>0.407</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4875</v>
+        <v>-1.4837</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4875</v>
+        <v>-0.7647</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2894</v>
+        <v>-1.8965</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9788</v>
+        <v>-1.7766</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3106</v>
+        <v>-0.1199</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5979</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5195</v>
+        <v>-0.1266</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1073</v>
+        <v>0.095</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4122</v>
+        <v>-0.2215</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.009</v>
+        <v>-2.7887</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3411</v>
+        <v>-4.0377</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3321</v>
+        <v>1.249</v>
       </c>
       <c r="G21" t="n">
         <v>-3.376</v>
@@ -2092,13 +2092,13 @@
         <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1028</v>
+        <v>-0.8825</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4388</v>
+        <v>-1.1354</v>
       </c>
       <c r="U21" t="n">
-        <v>0.336</v>
+        <v>0.2529</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8744</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3754</v>
+        <v>-3.0915</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9969</v>
+        <v>-1.7947</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3785</v>
+        <v>-1.2968</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5706</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4848</v>
+        <v>-0.2009</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1678</v>
+        <v>0.0344</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.317</v>
+        <v>-0.2353</v>
       </c>
       <c r="V22" t="n">
         <v>-3.1014</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5651</v>
+        <v>-5.4908</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6601</v>
+        <v>-3.3679</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.905</v>
+        <v>-2.1228</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9527</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2221</v>
+        <v>0.2965</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8778</v>
+        <v>0.17</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3444</v>
+        <v>0.1265</v>
       </c>
       <c r="V23" t="n">
         <v>-3.8113</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.018599999999998</v>
+        <v>-3.3443</v>
       </c>
       <c r="E24" t="n">
         <v>-7.9872</v>
       </c>
       <c r="F24" t="n">
-        <v>3.968900000000001</v>
+        <v>4.6429</v>
       </c>
       <c r="G24" t="n">
-        <v>7.439199999999998</v>
+        <v>7.4392</v>
       </c>
       <c r="H24" t="n">
-        <v>2.720500000000002</v>
+        <v>2.7205</v>
       </c>
       <c r="I24" t="n">
         <v>4.718699999999999</v>
@@ -2317,7 +2317,7 @@
         <v>-1.3552</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.953599999999999</v>
+        <v>-1.9536</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.5342</v>
@@ -2326,19 +2326,19 @@
         <v>17.5809</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.301899999999999</v>
+        <v>-2.6276</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.383099999999999</v>
+        <v>-3.3828</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08149999999999957</v>
+        <v>0.7556</v>
       </c>
       <c r="V24" t="n">
         <v>-6.2029</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2682</v>
+        <v>4.268200000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-10.4712</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484254_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484254_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,240 +714,260 @@
       </c>
       <c r="X3" t="n">
         <v>-0.6093</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1021</v>
+        <v>2.7349</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1833</v>
+        <v>2.7349</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2906</v>
+        <v>2.7349</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5454</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.836</v>
+        <v>2.4279</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9191</v>
+        <v>2.7349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7572</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1619</v>
+        <v>2.4279</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3026</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3893</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2642</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1251</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0454</v>
+        <v>1.1021</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2738</v>
+        <v>1.1833</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3192</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2288</v>
+        <v>0.2906</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2272</v>
+        <v>-0.5454</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9984</v>
+        <v>0.836</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2528</v>
+        <v>0.9191</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1719</v>
+        <v>0.7572</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0809</v>
+        <v>0.1619</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0241</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0553</v>
+        <v>-1.3026</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0793</v>
+        <v>0.6741</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.3893</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4635</v>
+        <v>0.2642</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4718</v>
+        <v>0.1251</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3869</v>
+        <v>-0.5545</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2908</v>
+        <v>1.0454</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3375</v>
+        <v>-0.2738</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0467</v>
+        <v>1.3192</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3917</v>
+        <v>1.2288</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3106</v>
+        <v>2.2272</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.9984</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4227</v>
+        <v>2.2528</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3057</v>
+        <v>2.1719</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7284</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8144</v>
+        <v>-1.0241</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0049</v>
+        <v>0.0553</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8095</v>
+        <v>-1.0793</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
         <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4134</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3653</v>
+        <v>-0.4635</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0481</v>
+        <v>0.4718</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6642</v>
+        <v>-0.3869</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -948,203 +978,213 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5138</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.935</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4213</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5656</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0934</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4722</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.797</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3252</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4718</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7685999999999999</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7682</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9932</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5614</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4318</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.758</v>
+        <v>-0.2908</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8418</v>
+        <v>-2.3375</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0838</v>
+        <v>2.0467</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8667</v>
+        <v>-0.3917</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4418</v>
+        <v>-0.3106</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3085</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0827</v>
+        <v>0.4227</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0422</v>
+        <v>-0.3057</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>0.7284</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9494</v>
+        <v>-0.8144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3996</v>
+        <v>-0.0049</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.349</v>
+        <v>-0.8095</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2222</v>
+        <v>0.4134</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0529</v>
+        <v>0.3653</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2751</v>
+        <v>0.0481</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2063</v>
+        <v>-0.758</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.042</v>
+        <v>-1.8418</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8358</v>
+        <v>1.0838</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7652</v>
+        <v>-0.8667</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.765</v>
+        <v>0.4418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0002</v>
+        <v>-1.3085</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6569</v>
+        <v>0.0827</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7921</v>
+        <v>0.0422</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1352</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1083</v>
+        <v>-0.9494</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9729</v>
+        <v>0.3996</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1354</v>
+        <v>-1.349</v>
       </c>
       <c r="P9" t="n">
         <v>-0.3907</v>
@@ -1156,496 +1196,527 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9533</v>
+        <v>0.2222</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7635999999999999</v>
+        <v>-0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1897</v>
+        <v>0.2751</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9962</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9962</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4465</v>
+        <v>-0.8208</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0544</v>
+        <v>-2.242</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3921</v>
+        <v>1.4213</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4762</v>
+        <v>-2.8726</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3602</v>
+        <v>-2.4004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8364</v>
+        <v>-0.4722</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7942</v>
+        <v>-2.104</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5526</v>
+        <v>-1.6322</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2416</v>
+        <v>-0.4718</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.318</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9127</v>
+        <v>-0.7682</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4052</v>
+        <v>-0.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0159</v>
+        <v>0.9932</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4023</v>
+        <v>0.5614</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3864</v>
+        <v>0.4318</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7671</v>
+        <v>-1.2063</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9746</v>
+        <v>-3.042</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7925</v>
+        <v>1.8358</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7004</v>
+        <v>-2.7652</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2576</v>
+        <v>-2.765</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4428</v>
+        <v>-0.0002</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.672</v>
+        <v>-1.6569</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6357</v>
+        <v>-1.7921</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3077</v>
+        <v>0.1352</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0283</v>
+        <v>-1.1083</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8933</v>
+        <v>-0.9729</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.135</v>
+        <v>-0.1354</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0151</v>
+        <v>0.9533</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3026</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3177</v>
+        <v>0.1897</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0.9962</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>0.9962</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9149</v>
+        <v>-1.7671</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6555</v>
+        <v>-0.9746</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2594</v>
+        <v>-0.7925</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.541</v>
+        <v>-1.7004</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4768</v>
+        <v>-0.2576</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0641</v>
+        <v>-1.4428</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1728</v>
+        <v>-0.672</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0819</v>
+        <v>0.6357</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2546</v>
+        <v>-1.3077</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3682</v>
+        <v>-1.0283</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5587</v>
+        <v>-0.8933</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8095</v>
+        <v>-0.135</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0186</v>
+        <v>0.0151</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4121</v>
+        <v>-0.3026</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4307</v>
+        <v>0.3177</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.926399999999999</v>
+        <v>-3.9149</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0608</v>
+        <v>-0.6555</v>
       </c>
       <c r="F13" t="n">
-        <v>7.987400000000001</v>
+        <v>-3.2594</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.439399999999999</v>
+        <v>-1.541</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.720699999999999</v>
+        <v>-0.4768</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.718599999999999</v>
+        <v>-1.0641</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2225</v>
+        <v>-0.1728</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8674</v>
+        <v>0.0819</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3552</v>
+        <v>-0.2546</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.6618</v>
+        <v>-1.3682</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.5879</v>
+        <v>-0.5587</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.073699999999999</v>
+        <v>-0.8095</v>
       </c>
       <c r="P13" t="n">
-        <v>1.953299999999999</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5809</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5343</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2093</v>
+        <v>-0.0186</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8264</v>
+        <v>0.4121</v>
       </c>
       <c r="U13" t="n">
-        <v>3.383</v>
+        <v>-0.4307</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2028</v>
+        <v>-2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>10.4709</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.2682</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7089</v>
+        <v>-4.1815</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1013</v>
+        <v>-3.7893</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6075</v>
+        <v>-0.3921</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4895</v>
+        <v>-2.2587</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4362</v>
+        <v>-0.6672</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0533</v>
+        <v>-1.5916</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8445</v>
+        <v>-0.9407</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1162</v>
+        <v>0.2456</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7284</v>
+        <v>-1.1863</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.355</v>
+        <v>-1.318</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3201</v>
+        <v>-0.9127</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6751</v>
+        <v>-0.4052</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.3208</v>
+        <v>-4.8836</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3398</v>
+        <v>-0.0159</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4689</v>
+        <v>-0.4023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1292</v>
+        <v>0.3864</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3405</v>
+        <v>1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0466</v>
+        <v>2.4373</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7061</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8177</v>
+        <v>4.926300000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4775</v>
+        <v>-3.060799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3402</v>
+        <v>7.9874</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9703</v>
+        <v>-7.4394</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5597</v>
+        <v>-2.7207</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4106</v>
+        <v>-4.718699999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1296</v>
+        <v>3.222500000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3929</v>
+        <v>1.8674</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7367</v>
+        <v>1.355200000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1593</v>
+        <v>-10.6618</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-4.587899999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6739000000000001</v>
+        <v>-6.073699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.9533</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-17.5809</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>19.5343</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5433</v>
+        <v>4.2093</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6987</v>
+        <v>0.8263999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1554</v>
+        <v>3.383</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>6.2028</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>10.4709</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
-      </c>
+        <v>-4.2682</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.97</v>
+        <v>4.7089</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6045</v>
+        <v>4.1013</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3655</v>
+        <v>0.6075</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4733</v>
+        <v>4.4895</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3387</v>
+        <v>4.4362</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1346</v>
+        <v>0.0533</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5822</v>
+        <v>4.8445</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9071</v>
+        <v>4.1162</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6751</v>
+        <v>0.7284</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1089</v>
+        <v>-0.355</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5684</v>
+        <v>0.3201</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5405</v>
+        <v>-0.6751</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-3.3208</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1555</v>
+        <v>-0.3398</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7853</v>
+        <v>-0.4689</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6299</v>
+        <v>0.1292</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8242</v>
+        <v>1.3405</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7145</v>
+        <v>3.0466</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1097</v>
+        <v>-1.7061</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1744</v>
+        <v>3.8177</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7608</v>
+        <v>2.4775</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5864</v>
+        <v>1.3402</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7514</v>
+        <v>4.9703</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0808</v>
+        <v>0.5597</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8322</v>
+        <v>4.4106</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7064</v>
+        <v>5.1296</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1433</v>
+        <v>1.3929</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5632</v>
+        <v>3.7367</v>
       </c>
       <c r="M17" t="n">
-        <v>0.045</v>
+        <v>-0.1593</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2241</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.269</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.3208</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6803</v>
+        <v>-0.5433</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1464</v>
+        <v>-0.6987</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5339</v>
+        <v>0.1554</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4875</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4875</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ALEN GARCIA</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4896</v>
+        <v>2.97</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0605</v>
+        <v>0.6045</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4291</v>
+        <v>2.3655</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4745</v>
+        <v>1.4733</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2047</v>
+        <v>1.3387</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2698</v>
+        <v>0.1346</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.5822</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.9071</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6751</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4745</v>
+        <v>-1.1089</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2047</v>
+        <v>-0.5684</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>-0.5405</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0151</v>
+        <v>-0.1555</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0605</v>
+        <v>-0.7853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0454</v>
+        <v>0.6299</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.8242</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9094</v>
+        <v>-0.1744</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3723</v>
+        <v>-0.7608</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4629</v>
+        <v>0.5864</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7264</v>
+        <v>2.7514</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9939</v>
+        <v>-0.0808</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2675</v>
+        <v>2.8322</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0312</v>
+        <v>2.7064</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2975</v>
+        <v>0.1433</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2663</v>
+        <v>2.5632</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3048</v>
+        <v>0.045</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3036</v>
+        <v>-0.2241</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0012</v>
+        <v>0.269</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.2975</v>
+        <v>-3.3208</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0199</v>
+        <v>-0.6803</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.387</v>
+        <v>-0.1464</v>
       </c>
       <c r="U19" t="n">
-        <v>0.407</v>
+        <v>-0.5339</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4837</v>
+        <v>-0.4875</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7647</v>
+        <v>-0.4875</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>F. ALEN GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8965</v>
+        <v>-0.4896</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7766</v>
+        <v>-0.0605</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1199</v>
+        <v>-0.4291</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5979</v>
+        <v>-0.4745</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3466</v>
+        <v>-0.2047</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9445</v>
+        <v>-0.2698</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6797</v>
+        <v>-0.4745</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2648</v>
+        <v>-0.2047</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9445</v>
+        <v>-0.2698</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1266</v>
+        <v>-0.0151</v>
       </c>
       <c r="T20" t="n">
-        <v>0.095</v>
+        <v>-0.0605</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2215</v>
+        <v>0.0454</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7887</v>
+        <v>-0.9094</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0377</v>
+        <v>-3.3723</v>
       </c>
       <c r="F21" t="n">
-        <v>1.249</v>
+        <v>2.4629</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.376</v>
+        <v>1.7264</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9036</v>
+        <v>2.9939</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4724</v>
+        <v>-1.2675</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4019</v>
+        <v>2.0312</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.47</v>
+        <v>3.2975</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06809999999999999</v>
+        <v>-1.2663</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9741</v>
+        <v>-0.3048</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4336</v>
+        <v>-0.3036</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5405</v>
+        <v>-0.0012</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3441</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3907</v>
+        <v>-4.2975</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7348</v>
+        <v>3.1255</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8825</v>
+        <v>0.0199</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1354</v>
+        <v>-0.387</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2529</v>
+        <v>0.407</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8744</v>
+        <v>-1.4837</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1097</v>
+        <v>-0.719</v>
       </c>
       <c r="X21" t="n">
         <v>-0.7647</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0915</v>
+        <v>-1.8965</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7947</v>
+        <v>-1.7766</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2968</v>
+        <v>-0.1199</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5706</v>
+        <v>-0.5979</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.921</v>
+        <v>0.3466</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3504</v>
+        <v>-0.9445</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1649</v>
+        <v>0.0819</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5718</v>
+        <v>0.0819</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5944</v>
+        <v>-0.6797</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3492</v>
+        <v>0.2648</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9435</v>
+        <v>-0.9445</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2009</v>
+        <v>-0.1266</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0344</v>
+        <v>0.095</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2353</v>
+        <v>-0.2215</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1014</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4908</v>
+        <v>-2.7887</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3679</v>
+        <v>-4.0377</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1228</v>
+        <v>1.249</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9527</v>
+        <v>-3.376</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8445</v>
+        <v>-2.9036</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1082</v>
+        <v>-0.4724</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1472</v>
+        <v>-2.4019</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.3091</v>
+        <v>-2.47</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1619</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1946</v>
+        <v>-0.9741</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4646</v>
+        <v>-0.4336</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.27</v>
+        <v>-0.5405</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>2.3441</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.3907</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2965</v>
+        <v>-0.8825</v>
       </c>
       <c r="T23" t="n">
-        <v>0.17</v>
+        <v>-1.1354</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1265</v>
+        <v>0.2529</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.8113</v>
+        <v>-0.8744</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.8113</v>
+        <v>-0.7647</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.0915</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.7947</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.2968</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.5706</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.921</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.1649</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5944</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.2009</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.2353</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.1014</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. GASPAR AGUILAR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.4908</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.3679</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.1228</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.9527</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.8445</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1082</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.1472</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-3.3091</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-3.8113</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-3.8113</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484254_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-3.3443</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-7.9872</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>4.6429</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>7.4392</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>2.7205</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>4.718699999999999</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>10.6618</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>4.588</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>6.073900000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-3.2223</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-1.8673</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-1.3552</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-1.9536</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-19.5342</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-2.6276</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-3.3828</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>0.7556</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>-6.2029</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>4.268200000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-10.4712</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
